--- a/docs/accessibility/accessibility-test-cases.xlsx
+++ b/docs/accessibility/accessibility-test-cases.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automated Accessibility" sheetId="1" r:id="R04eb126a91954e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Accessibility" sheetId="2" r:id="Rf72ba21de54b406b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="3" r:id="Rabf8bbe2aeaa4b24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WCAG Coverage Matrix" sheetId="4" r:id="Rbe46465a79f645ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automated Accessibility" sheetId="1" r:id="R8f5b1c4a59c74f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual Accessibility" sheetId="2" r:id="Rcdee35da165d4a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data" sheetId="3" r:id="Rd3eb07a1a2dd4575"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WCAG Coverage Matrix" sheetId="4" r:id="Ra6bde643fb9a41bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -467,7 +467,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>6 planned TestNG cases; 13 required scans. No accessibility execution results.</x:v>
+        <x:v>6 implemented cases; 13 scans completed on 2026-10-09. PASS; incomplete review pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
@@ -566,10 +566,10 @@
         <x:v>Future Allure: case/state ID, URL, timestamp, environment, axe version/rule configuration, structured results, rule/impact/tags, affected nodes, incomplete and technical errors. No evidence exists yet.</x:v>
       </x:c>
       <x:c r="N6" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O6" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P6" s="6" t="str">
         <x:v>Not Evaluated</x:v>
@@ -621,10 +621,10 @@
         <x:v>Future Allure: case/state ID, URL, timestamp, environment, axe version/rule configuration, structured results, rule/impact/tags, affected nodes, incomplete and technical errors. No evidence exists yet.</x:v>
       </x:c>
       <x:c r="N7" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O7" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P7" s="11" t="str">
         <x:v>Not Evaluated</x:v>
@@ -675,10 +675,10 @@
         <x:v>Future Allure: case/state ID, URL, timestamp, environment, axe version/rule configuration, structured results, rule/impact/tags, affected nodes, incomplete and technical errors. No evidence exists yet.</x:v>
       </x:c>
       <x:c r="N8" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O8" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P8" s="6" t="str">
         <x:v>Not Evaluated</x:v>
@@ -732,10 +732,10 @@
         <x:v>Future Allure: case/state ID, URL, timestamp, environment, axe version/rule configuration, structured results, rule/impact/tags, affected nodes, incomplete and technical errors. No evidence exists yet.</x:v>
       </x:c>
       <x:c r="N9" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O9" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P9" s="11" t="str">
         <x:v>Not Evaluated</x:v>
@@ -785,10 +785,10 @@
         <x:v>Future Allure: case/state ID, URL, timestamp, environment, axe version/rule configuration, structured results, rule/impact/tags, affected nodes, incomplete and technical errors. No evidence exists yet.</x:v>
       </x:c>
       <x:c r="N10" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O10" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P10" s="6" t="str">
         <x:v>Not Evaluated</x:v>
@@ -838,10 +838,10 @@
         <x:v>Future Allure: case/state ID, URL, timestamp, environment, axe version/rule configuration, structured results, rule/impact/tags, affected nodes, incomplete and technical errors. No evidence exists yet.</x:v>
       </x:c>
       <x:c r="N11" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Implemented / Verified</x:v>
       </x:c>
       <x:c r="O11" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Executed</x:v>
       </x:c>
       <x:c r="P11" s="11" t="str">
         <x:v>Not Evaluated</x:v>
@@ -850,7 +850,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9efc46316140441f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R523b2807086040e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1381,7 +1381,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdddb6766b25e4832"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbe645a98e2f4ec4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1662,7 +1662,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R885ab80780924e45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8461e56ff5b4bbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1789,16 +1789,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K6" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L6" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M6" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N6" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag111 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O6" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/non-text-content.html</x:v>
@@ -1839,7 +1839,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K7" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -1848,7 +1848,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N7" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag121. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O7" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/audio-only-and-video-only-prerecorded.html</x:v>
@@ -1889,16 +1889,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K8" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L8" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M8" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N8" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag122 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O8" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/captions-prerecorded.html</x:v>
@@ -1939,7 +1939,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K9" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -1948,7 +1948,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N9" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag123. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O9" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/audio-description-or-media-alternative-prerecorded.html</x:v>
@@ -1989,7 +1989,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K10" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L10" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -1998,7 +1998,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N10" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag124. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O10" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/captions-live.html</x:v>
@@ -2039,7 +2039,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K11" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2048,7 +2048,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N11" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag125. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O11" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/audio-description-prerecorded.html</x:v>
@@ -2089,16 +2089,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K12" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L12" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M12" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N12" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag131 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O12" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/info-and-relationships.html</x:v>
@@ -2139,7 +2139,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K13" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L13" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2148,7 +2148,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N13" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag132. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O13" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/meaningful-sequence.html</x:v>
@@ -2189,7 +2189,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K14" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L14" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -2198,7 +2198,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N14" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag133. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O14" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/sensory-characteristics.html</x:v>
@@ -2239,16 +2239,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K15" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M15" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N15" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag134 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O15" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/orientation.html</x:v>
@@ -2289,16 +2289,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K16" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L16" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M16" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N16" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag135 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O16" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/identify-input-purpose.html</x:v>
@@ -2339,16 +2339,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K17" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M17" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N17" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag141 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O17" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/use-of-color.html</x:v>
@@ -2389,16 +2389,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K18" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L18" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M18" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N18" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag142 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O18" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/audio-control.html</x:v>
@@ -2439,16 +2439,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K19" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M19" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N19" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag143 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O19" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/contrast-minimum.html</x:v>
@@ -2489,16 +2489,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K20" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L20" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M20" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N20" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag144 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O20" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/resize-text.html</x:v>
@@ -2539,7 +2539,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K21" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2548,7 +2548,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N21" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag145. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O21" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/images-of-text.html</x:v>
@@ -2589,7 +2589,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K22" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L22" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -2598,7 +2598,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N22" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag1410. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O22" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/reflow.html</x:v>
@@ -2639,7 +2639,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K23" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2648,7 +2648,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N23" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag1411. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O23" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/non-text-contrast.html</x:v>
@@ -2689,16 +2689,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K24" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L24" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M24" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N24" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag1412 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O24" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/text-spacing.html</x:v>
@@ -2739,7 +2739,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K25" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2748,7 +2748,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N25" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag1413. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O25" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/content-on-hover-or-focus.html</x:v>
@@ -2789,16 +2789,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K26" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L26" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M26" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N26" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag211 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O26" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/keyboard.html</x:v>
@@ -2839,7 +2839,7 @@
         <x:v>The open side menu is included. Submenu expansion is not a separate required automated scan; excluded routes must not be entered.</x:v>
       </x:c>
       <x:c r="K27" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -2848,7 +2848,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N27" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag212. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O27" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/no-keyboard-trap.html</x:v>
@@ -2889,7 +2889,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K28" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L28" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -2898,7 +2898,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N28" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag214. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O28" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/character-key-shortcuts.html</x:v>
@@ -2939,16 +2939,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K29" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L29" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M29" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N29" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag221 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O29" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/timing-adjustable.html</x:v>
@@ -2989,16 +2989,16 @@
         <x:v>Applicable is retained from the source for the broader application. Evidence cited for the Slider is outside initial scope. Presence of triggering content in the approved flow is To Be Confirmed. Manual execution remains deferred for the excluded route.</x:v>
       </x:c>
       <x:c r="K30" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L30" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M30" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N30" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag222 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O30" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/pause-stop-hide.html</x:v>
@@ -3039,7 +3039,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K31" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3048,7 +3048,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N31" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag231. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O31" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/three-flashes-or-below-threshold.html</x:v>
@@ -3089,16 +3089,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K32" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L32" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M32" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N32" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag241 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O32" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/bypass-blocks.html</x:v>
@@ -3139,16 +3139,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K33" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L33" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M33" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N33" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag242 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O33" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/page-titled.html</x:v>
@@ -3189,7 +3189,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K34" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L34" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3198,7 +3198,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N34" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag243. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O34" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/focus-order.html</x:v>
@@ -3239,16 +3239,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K35" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L35" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M35" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N35" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag244 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O35" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/link-purpose-in-context.html</x:v>
@@ -3289,7 +3289,7 @@
         <x:v>Evaluate navigation within approved pages and document process exceptions. Detail and long/dynamic catalogs remain outside scope. No application-wide verdict.</x:v>
       </x:c>
       <x:c r="K36" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L36" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3298,7 +3298,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N36" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag245. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O36" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/multiple-ways.html</x:v>
@@ -3339,7 +3339,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K37" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L37" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3348,7 +3348,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N37" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag246. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O37" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/headings-and-labels.html</x:v>
@@ -3389,7 +3389,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K38" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L38" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3398,7 +3398,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N38" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag247. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O38" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/focus-visible.html</x:v>
@@ -3439,7 +3439,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K39" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L39" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3448,7 +3448,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N39" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag2411. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O39" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/focus-not-obscured-minimum.html</x:v>
@@ -3489,7 +3489,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K40" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L40" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3498,7 +3498,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N40" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag251. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O40" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/pointer-gestures.html</x:v>
@@ -3539,7 +3539,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K41" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L41" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3548,7 +3548,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N41" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag252. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O41" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/pointer-cancellation.html</x:v>
@@ -3589,16 +3589,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K42" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L42" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M42" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N42" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag253 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O42" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/label-in-name.html</x:v>
@@ -3639,7 +3639,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K43" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L43" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3648,7 +3648,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N43" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag254. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O43" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/motion-actuation.html</x:v>
@@ -3689,7 +3689,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K44" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L44" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3698,7 +3698,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N44" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag257. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O44" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/dragging-movements.html</x:v>
@@ -3739,16 +3739,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K45" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L45" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M45" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N45" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag258 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O45" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/target-size-minimum.html</x:v>
@@ -3789,16 +3789,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K46" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L46" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M46" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N46" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag311 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O46" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/language-of-page.html</x:v>
@@ -3839,16 +3839,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K47" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L47" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M47" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N47" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag312 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O47" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/language-of-parts.html</x:v>
@@ -3889,7 +3889,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K48" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L48" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3898,7 +3898,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N48" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag321. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O48" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/on-focus.html</x:v>
@@ -3939,7 +3939,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K49" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L49" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -3948,7 +3948,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N49" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag322. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O49" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/on-input.html</x:v>
@@ -3989,7 +3989,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K50" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L50" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -3998,7 +3998,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N50" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag323. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O50" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/consistent-navigation.html</x:v>
@@ -4039,7 +4039,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K51" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L51" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -4048,7 +4048,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N51" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag324. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O51" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/consistent-identification.html</x:v>
@@ -4089,7 +4089,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K52" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L52" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -4098,7 +4098,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N52" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag326. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O52" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/consistent-help.html</x:v>
@@ -4139,7 +4139,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K53" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L53" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -4148,7 +4148,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N53" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag331. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O53" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/error-identification.html</x:v>
@@ -4189,16 +4189,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K54" s="6" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L54" s="6" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M54" s="6" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N54" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag332 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O54" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/labels-or-instructions.html</x:v>
@@ -4239,7 +4239,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K55" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L55" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -4248,7 +4248,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N55" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag333. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O55" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/error-suggestion.html</x:v>
@@ -4289,7 +4289,7 @@
         <x:v>Assess order review and effects within the approved process. Reset App State effects remain an applicability question, not an extra automated scan.</x:v>
       </x:c>
       <x:c r="K56" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L56" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -4298,7 +4298,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N56" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag334. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O56" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/error-prevention-legal-financial-data.html</x:v>
@@ -4339,7 +4339,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K57" s="11" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L57" s="11" t="str">
         <x:v>Not Executed</x:v>
@@ -4348,7 +4348,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N57" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag337. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O57" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/redundant-entry.html</x:v>
@@ -4389,7 +4389,7 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K58" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L58" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -4398,7 +4398,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N58" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag338. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O58" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/accessible-authentication-minimum.html</x:v>
@@ -4439,16 +4439,16 @@
         <x:v>Evaluate approved states only. Additional functions and absent triggering content require confirmation. Test relationships describe planned partial coverage, not completed verification.</x:v>
       </x:c>
       <x:c r="K59" s="11" t="str">
-        <x:v>Planned / Not Implemented</x:v>
+        <x:v>Automation Implemented / Manual Planned</x:v>
       </x:c>
       <x:c r="L59" s="11" t="str">
-        <x:v>Not Executed</x:v>
+        <x:v>Partial Automated Execution / Manual Not Executed</x:v>
       </x:c>
       <x:c r="M59" s="11" t="str">
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N59" s="11" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: rules tagged wcag412 executed in linked states. See Test Results and execution-summary.json. Partial coverage; manual review pending. Criterion Not Evaluated. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O59" s="11" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/name-role-value.html</x:v>
@@ -4489,7 +4489,7 @@
         <x:v>Only errors and cart changes in approved states are planned. Spinner and other dynamic routes remain excluded.</x:v>
       </x:c>
       <x:c r="K60" s="6" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Manual Planned</x:v>
       </x:c>
       <x:c r="L60" s="6" t="str">
         <x:v>Not Executed</x:v>
@@ -4498,7 +4498,7 @@
         <x:v>Not Evaluated</x:v>
       </x:c>
       <x:c r="N60" s="6" t="str">
-        <x:v>REF-02 §2 (embedded in Test Data, REF-02): historical static observations are reproduced in this row and its scope clarification, not rendered-state test results. No axe/NVDA/manual execution evidence. Confirm applicability and evaluate within approved scope; inspection date/build reference were not recorded.</x:v>
+        <x:v>axe 4.13.0: no selected rule tagged wcag413. Provisional links do not establish criterion execution. Manual evaluation Planned / Not Executed. REF-02 retains historical observations.</x:v>
       </x:c>
       <x:c r="O60" s="6" t="str">
         <x:v>https://www.w3.org/WAI/WCAG22/Understanding/status-messages.html</x:v>
@@ -4518,7 +4518,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c4a63a8c6174395"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdec4aa3656b54d77"/>
   </x:tableParts>
 </x:worksheet>
 </file>